--- a/StructureDefinition-ophthalmic-specular-microscopy.xlsx
+++ b/StructureDefinition-ophthalmic-specular-microscopy.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$150</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$159</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5827" uniqueCount="608">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6176" uniqueCount="629">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T17:43:23+00:00</t>
+    <t>2026-09-11T00:16:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1612,6 +1612,48 @@
     <t>Observation.component:capturePos.referenceRange</t>
   </si>
   <si>
+    <t>Observation.component:analysisMethod</t>
+  </si>
+  <si>
+    <t>analysisMethod</t>
+  </si>
+  <si>
+    <t>Observation.component:analysisMethod.id</t>
+  </si>
+  <si>
+    <t>Observation.component:analysisMethod.extension</t>
+  </si>
+  <si>
+    <t>Observation.component:analysisMethod.modifierExtension</t>
+  </si>
+  <si>
+    <t>Observation.component:analysisMethod.code</t>
+  </si>
+  <si>
+    <t>Analysis method type - LOINC 100086-8 (OD) / 100155-1 (OS)</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://loinc.org"/&gt;
+    &lt;code value="100086-8"/&gt;
+    &lt;display value="Right cornea Type of Analysis method by Specular microscopy"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>Observation.component:analysisMethod.value[x]</t>
+  </si>
+  <si>
+    <t>Observation.component:analysisMethod.dataAbsentReason</t>
+  </si>
+  <si>
+    <t>Observation.component:analysisMethod.interpretation</t>
+  </si>
+  <si>
+    <t>Observation.component:analysisMethod.referenceRange</t>
+  </si>
+  <si>
     <t>Observation.component:density</t>
   </si>
   <si>
@@ -1630,7 +1672,16 @@
     <t>Observation.component:density.code</t>
   </si>
   <si>
-    <t>Endothelial cell density (CD) - endothelial cell count</t>
+    <t>Endothelial cell density (CD) - LOINC 100070-2 (OD) / 100071-0 (OS)</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://loinc.org"/&gt;
+    &lt;code value="100070-2"/&gt;
+    &lt;display value="Right cornea Cell density"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
     <t>Observation.component:density.value[x]</t>
@@ -1667,7 +1718,16 @@
     <t>Observation.component:cellCount.code</t>
   </si>
   <si>
-    <t>Number of cells analyzed (N) - total cells counted in analysis area</t>
+    <t>Number of cells analyzed (N) - LOINC 100076-9 (OD) / 100077-7 (OS)</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://loinc.org"/&gt;
+    &lt;code value="100076-9"/&gt;
+    &lt;display value="Right cornea Endothelial cells counted"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
     <t>Observation.component:cellCount.value[x]</t>
@@ -1700,7 +1760,16 @@
     <t>Observation.component:cv.code</t>
   </si>
   <si>
-    <t>Coefficient of variation (CV) - cell size variability (polymegathism), normal &lt;40%</t>
+    <t>Coefficient of variation (CV) - LOINC 100072-8 (OD) / 100073-6 (OS), normal &lt;40%</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://loinc.org"/&gt;
+    &lt;code value="100072-8"/&gt;
+    &lt;display value="Right cornea Coefficient of variation"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
     <t>Observation.component:cv.value[x]</t>
@@ -1733,7 +1802,16 @@
     <t>Observation.component:hexagonality.code</t>
   </si>
   <si>
-    <t>Hexagonality (HEX) - percentage of hexagonal cells (pleomorphism), normal &gt;50%</t>
+    <t>Hexagonality (HEX) - LOINC 100074-4 (OD) / 100075-1 (OS), normal &gt;50%</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://loinc.org"/&gt;
+    &lt;code value="100074-4"/&gt;
+    &lt;display value="Right cornea Hexagonality"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
     <t>Observation.component:hexagonality.value[x]</t>
@@ -1766,7 +1844,16 @@
     <t>Observation.component:cct.code</t>
   </si>
   <si>
-    <t>Central corneal thickness (CCT) - CCT measured by specular</t>
+    <t>Central corneal thickness (CCT) - LOINC 79825-6 (OD) / 79826-4 (OS)</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://loinc.org"/&gt;
+    &lt;code value="79825-6"/&gt;
+    &lt;display value="Right cornea Central corneal thickness Pachymetry"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
     <t>Observation.component:cct.value[x]</t>
@@ -1799,7 +1886,16 @@
     <t>Observation.component:minArea.code</t>
   </si>
   <si>
-    <t>Minimum cell area (MIN) - smallest cell area measured</t>
+    <t>Minimum cell area (MIN) - LOINC 100078-5 (OD) / 100079-3 (OS)</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://loinc.org"/&gt;
+    &lt;code value="100078-5"/&gt;
+    &lt;display value="Right cornea Endothelial cell area.min"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
     <t>Observation.component:minArea.value[x]</t>
@@ -1832,7 +1928,16 @@
     <t>Observation.component:maxArea.code</t>
   </si>
   <si>
-    <t>Maximum cell area (MAX) - largest cell area measured</t>
+    <t>Maximum cell area (MAX) - LOINC 100080-1 (OD) / 100081-9 (OS)</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://loinc.org"/&gt;
+    &lt;code value="100080-1"/&gt;
+    &lt;display value="Right cornea Endothelial cell area.max"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
     <t>Observation.component:maxArea.value[x]</t>
@@ -1865,7 +1970,16 @@
     <t>Observation.component:avgArea.code</t>
   </si>
   <si>
-    <t>Average cell area (AVG) - mean cell area</t>
+    <t>Average cell area (AVG) - LOINC 100082-7 (OD) / 100083-5 (OS)</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://loinc.org"/&gt;
+    &lt;code value="100082-7"/&gt;
+    &lt;display value="Right cornea Endothelial cell area.mean"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
     <t>Observation.component:avgArea.value[x]</t>
@@ -1898,7 +2012,16 @@
     <t>Observation.component:sdArea.code</t>
   </si>
   <si>
-    <t>Cell area SD - standard deviation of cell area</t>
+    <t>Cell area SD - LOINC 100084-3 (OD) / 100085-0 (OS)</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://loinc.org"/&gt;
+    &lt;code value="100084-3"/&gt;
+    &lt;display value="Right cornea Cell area.standard deviation"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
     <t>Observation.component:sdArea.value[x]</t>
@@ -2235,12 +2358,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP150"/>
+  <dimension ref="A1:AP159"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="45.890625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="47.95703125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="38.30078125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.08984375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="13.15234375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -10626,7 +10749,7 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G70" t="s" s="2">
         <v>94</v>
@@ -11145,7 +11268,7 @@
         <v>83</v>
       </c>
       <c r="S74" t="s" s="2">
-        <v>83</v>
+        <v>515</v>
       </c>
       <c r="T74" t="s" s="2">
         <v>83</v>
@@ -11219,7 +11342,7 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B75" t="s" s="2">
         <v>485</v>
@@ -11245,7 +11368,7 @@
         <v>95</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>516</v>
+        <v>192</v>
       </c>
       <c r="L75" t="s" s="2">
         <v>486</v>
@@ -11720,7 +11843,7 @@
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G79" t="s" s="2">
         <v>94</v>
@@ -12239,7 +12362,7 @@
         <v>83</v>
       </c>
       <c r="S83" t="s" s="2">
-        <v>83</v>
+        <v>527</v>
       </c>
       <c r="T83" t="s" s="2">
         <v>83</v>
@@ -12313,7 +12436,7 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B84" t="s" s="2">
         <v>485</v>
@@ -12339,7 +12462,7 @@
         <v>95</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>516</v>
+        <v>529</v>
       </c>
       <c r="L84" t="s" s="2">
         <v>486</v>
@@ -12435,7 +12558,7 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B85" t="s" s="2">
         <v>489</v>
@@ -12557,7 +12680,7 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B86" t="s" s="2">
         <v>493</v>
@@ -12679,7 +12802,7 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B87" t="s" s="2">
         <v>494</v>
@@ -12801,13 +12924,13 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B88" t="s" s="2">
         <v>469</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="D88" t="s" s="2">
         <v>83</v>
@@ -12925,7 +13048,7 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B89" t="s" s="2">
         <v>477</v>
@@ -13043,7 +13166,7 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B90" t="s" s="2">
         <v>478</v>
@@ -13163,7 +13286,7 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B91" t="s" s="2">
         <v>479</v>
@@ -13285,7 +13408,7 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B92" t="s" s="2">
         <v>480</v>
@@ -13314,7 +13437,7 @@
         <v>192</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="M92" t="s" s="2">
         <v>482</v>
@@ -13333,7 +13456,7 @@
         <v>83</v>
       </c>
       <c r="S92" t="s" s="2">
-        <v>83</v>
+        <v>540</v>
       </c>
       <c r="T92" t="s" s="2">
         <v>83</v>
@@ -13407,7 +13530,7 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="B93" t="s" s="2">
         <v>485</v>
@@ -13433,7 +13556,7 @@
         <v>95</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>516</v>
+        <v>529</v>
       </c>
       <c r="L93" t="s" s="2">
         <v>486</v>
@@ -13529,7 +13652,7 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="B94" t="s" s="2">
         <v>489</v>
@@ -13651,7 +13774,7 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="B95" t="s" s="2">
         <v>493</v>
@@ -13773,7 +13896,7 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="B96" t="s" s="2">
         <v>494</v>
@@ -13895,13 +14018,13 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="B97" t="s" s="2">
         <v>469</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="D97" t="s" s="2">
         <v>83</v>
@@ -14019,7 +14142,7 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="B98" t="s" s="2">
         <v>477</v>
@@ -14137,7 +14260,7 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="B99" t="s" s="2">
         <v>478</v>
@@ -14257,7 +14380,7 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="B100" t="s" s="2">
         <v>479</v>
@@ -14379,7 +14502,7 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="B101" t="s" s="2">
         <v>480</v>
@@ -14408,7 +14531,7 @@
         <v>192</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="M101" t="s" s="2">
         <v>482</v>
@@ -14427,7 +14550,7 @@
         <v>83</v>
       </c>
       <c r="S101" t="s" s="2">
-        <v>83</v>
+        <v>552</v>
       </c>
       <c r="T101" t="s" s="2">
         <v>83</v>
@@ -14501,7 +14624,7 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="B102" t="s" s="2">
         <v>485</v>
@@ -14527,7 +14650,7 @@
         <v>95</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>516</v>
+        <v>529</v>
       </c>
       <c r="L102" t="s" s="2">
         <v>486</v>
@@ -14623,7 +14746,7 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="B103" t="s" s="2">
         <v>489</v>
@@ -14745,7 +14868,7 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="B104" t="s" s="2">
         <v>493</v>
@@ -14867,7 +14990,7 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="B105" t="s" s="2">
         <v>494</v>
@@ -14989,13 +15112,13 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="B106" t="s" s="2">
         <v>469</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="D106" t="s" s="2">
         <v>83</v>
@@ -15113,7 +15236,7 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="B107" t="s" s="2">
         <v>477</v>
@@ -15231,7 +15354,7 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="B108" t="s" s="2">
         <v>478</v>
@@ -15351,7 +15474,7 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="B109" t="s" s="2">
         <v>479</v>
@@ -15473,7 +15596,7 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="B110" t="s" s="2">
         <v>480</v>
@@ -15502,7 +15625,7 @@
         <v>192</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="M110" t="s" s="2">
         <v>482</v>
@@ -15521,7 +15644,7 @@
         <v>83</v>
       </c>
       <c r="S110" t="s" s="2">
-        <v>83</v>
+        <v>564</v>
       </c>
       <c r="T110" t="s" s="2">
         <v>83</v>
@@ -15595,7 +15718,7 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="B111" t="s" s="2">
         <v>485</v>
@@ -15621,7 +15744,7 @@
         <v>95</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>516</v>
+        <v>529</v>
       </c>
       <c r="L111" t="s" s="2">
         <v>486</v>
@@ -15717,7 +15840,7 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="B112" t="s" s="2">
         <v>489</v>
@@ -15839,7 +15962,7 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="B113" t="s" s="2">
         <v>493</v>
@@ -15961,7 +16084,7 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="B114" t="s" s="2">
         <v>494</v>
@@ -16083,13 +16206,13 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="B115" t="s" s="2">
         <v>469</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="D115" t="s" s="2">
         <v>83</v>
@@ -16207,7 +16330,7 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="B116" t="s" s="2">
         <v>477</v>
@@ -16325,7 +16448,7 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="B117" t="s" s="2">
         <v>478</v>
@@ -16445,7 +16568,7 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="B118" t="s" s="2">
         <v>479</v>
@@ -16567,7 +16690,7 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="B119" t="s" s="2">
         <v>480</v>
@@ -16596,7 +16719,7 @@
         <v>192</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="M119" t="s" s="2">
         <v>482</v>
@@ -16615,7 +16738,7 @@
         <v>83</v>
       </c>
       <c r="S119" t="s" s="2">
-        <v>83</v>
+        <v>576</v>
       </c>
       <c r="T119" t="s" s="2">
         <v>83</v>
@@ -16689,7 +16812,7 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="B120" t="s" s="2">
         <v>485</v>
@@ -16715,7 +16838,7 @@
         <v>95</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>516</v>
+        <v>529</v>
       </c>
       <c r="L120" t="s" s="2">
         <v>486</v>
@@ -16811,7 +16934,7 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="B121" t="s" s="2">
         <v>489</v>
@@ -16933,7 +17056,7 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="B122" t="s" s="2">
         <v>493</v>
@@ -17055,7 +17178,7 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="B123" t="s" s="2">
         <v>494</v>
@@ -17177,13 +17300,13 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="B124" t="s" s="2">
         <v>469</v>
       </c>
       <c r="C124" t="s" s="2">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="D124" t="s" s="2">
         <v>83</v>
@@ -17301,7 +17424,7 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="B125" t="s" s="2">
         <v>477</v>
@@ -17419,7 +17542,7 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="B126" t="s" s="2">
         <v>478</v>
@@ -17539,7 +17662,7 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="B127" t="s" s="2">
         <v>479</v>
@@ -17661,7 +17784,7 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="B128" t="s" s="2">
         <v>480</v>
@@ -17690,7 +17813,7 @@
         <v>192</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="M128" t="s" s="2">
         <v>482</v>
@@ -17709,7 +17832,7 @@
         <v>83</v>
       </c>
       <c r="S128" t="s" s="2">
-        <v>83</v>
+        <v>588</v>
       </c>
       <c r="T128" t="s" s="2">
         <v>83</v>
@@ -17783,7 +17906,7 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>582</v>
+        <v>589</v>
       </c>
       <c r="B129" t="s" s="2">
         <v>485</v>
@@ -17809,7 +17932,7 @@
         <v>95</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>516</v>
+        <v>529</v>
       </c>
       <c r="L129" t="s" s="2">
         <v>486</v>
@@ -17905,7 +18028,7 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>583</v>
+        <v>590</v>
       </c>
       <c r="B130" t="s" s="2">
         <v>489</v>
@@ -18027,7 +18150,7 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>584</v>
+        <v>591</v>
       </c>
       <c r="B131" t="s" s="2">
         <v>493</v>
@@ -18149,7 +18272,7 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="B132" t="s" s="2">
         <v>494</v>
@@ -18271,13 +18394,13 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>586</v>
+        <v>593</v>
       </c>
       <c r="B133" t="s" s="2">
         <v>469</v>
       </c>
       <c r="C133" t="s" s="2">
-        <v>587</v>
+        <v>594</v>
       </c>
       <c r="D133" t="s" s="2">
         <v>83</v>
@@ -18395,7 +18518,7 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>588</v>
+        <v>595</v>
       </c>
       <c r="B134" t="s" s="2">
         <v>477</v>
@@ -18513,7 +18636,7 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>589</v>
+        <v>596</v>
       </c>
       <c r="B135" t="s" s="2">
         <v>478</v>
@@ -18633,7 +18756,7 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>590</v>
+        <v>597</v>
       </c>
       <c r="B136" t="s" s="2">
         <v>479</v>
@@ -18755,7 +18878,7 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>591</v>
+        <v>598</v>
       </c>
       <c r="B137" t="s" s="2">
         <v>480</v>
@@ -18784,7 +18907,7 @@
         <v>192</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>592</v>
+        <v>599</v>
       </c>
       <c r="M137" t="s" s="2">
         <v>482</v>
@@ -18803,7 +18926,7 @@
         <v>83</v>
       </c>
       <c r="S137" t="s" s="2">
-        <v>83</v>
+        <v>600</v>
       </c>
       <c r="T137" t="s" s="2">
         <v>83</v>
@@ -18877,7 +19000,7 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>593</v>
+        <v>601</v>
       </c>
       <c r="B138" t="s" s="2">
         <v>485</v>
@@ -18903,7 +19026,7 @@
         <v>95</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>516</v>
+        <v>529</v>
       </c>
       <c r="L138" t="s" s="2">
         <v>486</v>
@@ -18999,7 +19122,7 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>594</v>
+        <v>602</v>
       </c>
       <c r="B139" t="s" s="2">
         <v>489</v>
@@ -19121,7 +19244,7 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>595</v>
+        <v>603</v>
       </c>
       <c r="B140" t="s" s="2">
         <v>493</v>
@@ -19243,7 +19366,7 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>596</v>
+        <v>604</v>
       </c>
       <c r="B141" t="s" s="2">
         <v>494</v>
@@ -19365,13 +19488,13 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>597</v>
+        <v>605</v>
       </c>
       <c r="B142" t="s" s="2">
         <v>469</v>
       </c>
       <c r="C142" t="s" s="2">
-        <v>598</v>
+        <v>606</v>
       </c>
       <c r="D142" t="s" s="2">
         <v>83</v>
@@ -19489,7 +19612,7 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="B143" t="s" s="2">
         <v>477</v>
@@ -19607,7 +19730,7 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>600</v>
+        <v>608</v>
       </c>
       <c r="B144" t="s" s="2">
         <v>478</v>
@@ -19727,7 +19850,7 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="B145" t="s" s="2">
         <v>479</v>
@@ -19849,7 +19972,7 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>602</v>
+        <v>610</v>
       </c>
       <c r="B146" t="s" s="2">
         <v>480</v>
@@ -19878,7 +20001,7 @@
         <v>192</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>603</v>
+        <v>611</v>
       </c>
       <c r="M146" t="s" s="2">
         <v>482</v>
@@ -19897,7 +20020,7 @@
         <v>83</v>
       </c>
       <c r="S146" t="s" s="2">
-        <v>83</v>
+        <v>612</v>
       </c>
       <c r="T146" t="s" s="2">
         <v>83</v>
@@ -19971,7 +20094,7 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>604</v>
+        <v>613</v>
       </c>
       <c r="B147" t="s" s="2">
         <v>485</v>
@@ -19997,7 +20120,7 @@
         <v>95</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>516</v>
+        <v>529</v>
       </c>
       <c r="L147" t="s" s="2">
         <v>486</v>
@@ -20093,7 +20216,7 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>605</v>
+        <v>614</v>
       </c>
       <c r="B148" t="s" s="2">
         <v>489</v>
@@ -20215,7 +20338,7 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>606</v>
+        <v>615</v>
       </c>
       <c r="B149" t="s" s="2">
         <v>493</v>
@@ -20337,7 +20460,7 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>607</v>
+        <v>616</v>
       </c>
       <c r="B150" t="s" s="2">
         <v>494</v>
@@ -20457,8 +20580,1102 @@
         <v>83</v>
       </c>
     </row>
+    <row r="151">
+      <c r="A151" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="B151" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="C151" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="D151" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E151" s="2"/>
+      <c r="F151" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G151" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H151" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I151" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J151" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K151" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="L151" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="M151" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="N151" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="O151" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="P151" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q151" s="2"/>
+      <c r="R151" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S151" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T151" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U151" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V151" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W151" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X151" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y151" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z151" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA151" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB151" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC151" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD151" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE151" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF151" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AG151" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI151" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ151" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK151" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL151" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM151" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AN151" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AO151" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP151" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="152" hidden="true">
+      <c r="A152" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="B152" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="C152" s="2"/>
+      <c r="D152" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E152" s="2"/>
+      <c r="F152" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G152" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H152" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I152" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J152" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K152" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="L152" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="M152" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="N152" s="2"/>
+      <c r="O152" s="2"/>
+      <c r="P152" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q152" s="2"/>
+      <c r="R152" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S152" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T152" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U152" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V152" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W152" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X152" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y152" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z152" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA152" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB152" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC152" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD152" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE152" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF152" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AG152" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH152" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI152" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ152" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AK152" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL152" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM152" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN152" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AO152" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP152" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="153" hidden="true">
+      <c r="A153" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="B153" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="C153" s="2"/>
+      <c r="D153" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="E153" s="2"/>
+      <c r="F153" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H153" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I153" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J153" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K153" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L153" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="M153" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="N153" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O153" s="2"/>
+      <c r="P153" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q153" s="2"/>
+      <c r="R153" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S153" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T153" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U153" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V153" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W153" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X153" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y153" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z153" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA153" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB153" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC153" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD153" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE153" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF153" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AG153" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI153" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ153" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK153" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL153" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM153" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN153" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AO153" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP153" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="154" hidden="true">
+      <c r="A154" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="B154" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="C154" s="2"/>
+      <c r="D154" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="E154" s="2"/>
+      <c r="F154" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G154" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H154" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I154" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="J154" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K154" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L154" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="M154" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="N154" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O154" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="P154" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q154" s="2"/>
+      <c r="R154" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S154" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T154" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U154" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V154" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W154" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X154" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y154" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z154" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA154" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB154" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC154" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD154" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE154" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF154" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AG154" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH154" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI154" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ154" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK154" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL154" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM154" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN154" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AO154" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP154" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="155" hidden="true">
+      <c r="A155" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="B155" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="C155" s="2"/>
+      <c r="D155" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E155" s="2"/>
+      <c r="F155" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G155" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H155" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I155" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J155" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K155" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L155" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="M155" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="N155" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="O155" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="P155" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q155" s="2"/>
+      <c r="R155" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S155" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="T155" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U155" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V155" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W155" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X155" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="Y155" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="Z155" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="AA155" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB155" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC155" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD155" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE155" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF155" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AG155" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AH155" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI155" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ155" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK155" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL155" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AM155" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AN155" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AO155" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AP155" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="156" hidden="true">
+      <c r="A156" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="B156" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="C156" s="2"/>
+      <c r="D156" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E156" s="2"/>
+      <c r="F156" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G156" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H156" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I156" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J156" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K156" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="L156" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="M156" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="N156" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="O156" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="P156" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q156" s="2"/>
+      <c r="R156" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S156" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T156" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U156" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V156" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W156" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X156" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y156" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z156" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA156" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB156" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC156" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD156" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE156" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF156" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="AG156" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH156" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI156" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ156" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK156" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL156" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AM156" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AN156" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AO156" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP156" t="s" s="2">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="157" hidden="true">
+      <c r="A157" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="B157" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="C157" s="2"/>
+      <c r="D157" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E157" s="2"/>
+      <c r="F157" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G157" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H157" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I157" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J157" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K157" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L157" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="M157" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="N157" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="O157" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="P157" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q157" s="2"/>
+      <c r="R157" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S157" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T157" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U157" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V157" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W157" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X157" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="Y157" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="Z157" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="AA157" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB157" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC157" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD157" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE157" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF157" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AG157" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH157" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI157" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AJ157" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK157" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL157" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM157" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AN157" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AO157" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP157" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="158" hidden="true">
+      <c r="A158" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="B158" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="C158" s="2"/>
+      <c r="D158" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="E158" s="2"/>
+      <c r="F158" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G158" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H158" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I158" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J158" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K158" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L158" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="M158" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="N158" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="O158" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="P158" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q158" s="2"/>
+      <c r="R158" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S158" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T158" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U158" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V158" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W158" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X158" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="Y158" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="Z158" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="AA158" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB158" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC158" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD158" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE158" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF158" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="AG158" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH158" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI158" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ158" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK158" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL158" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AM158" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AN158" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AO158" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP158" t="s" s="2">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="159" hidden="true">
+      <c r="A159" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="B159" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="C159" s="2"/>
+      <c r="D159" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E159" s="2"/>
+      <c r="F159" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G159" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H159" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I159" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J159" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K159" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="L159" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="M159" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="N159" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="O159" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="P159" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q159" s="2"/>
+      <c r="R159" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S159" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T159" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U159" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V159" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W159" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X159" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y159" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z159" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA159" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB159" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC159" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD159" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE159" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF159" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="AG159" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH159" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI159" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ159" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK159" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL159" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM159" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AN159" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AO159" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP159" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AP150">
+  <autoFilter ref="A1:AP159">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -20468,7 +21685,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI149">
+  <conditionalFormatting sqref="A2:AI158">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-ophthalmic-specular-microscopy.xlsx
+++ b/StructureDefinition-ophthalmic-specular-microscopy.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T00:16:12+00:00</t>
+    <t>2026-10-19T22:17:00-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2361,17 +2361,17 @@
   <dimension ref="A1:AP159"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="47.95703125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="38.30078125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="13.15234375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="49.28515625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="39.10546875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="13.640625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.8125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.29296875" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.21484375" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.55078125" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="122.43359375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="129.546875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2380,28 +2380,28 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="54.6171875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="47.7421875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="35.16796875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="7.93359375" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.08984375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="14.4296875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="54.2734375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="50.55078125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.10546875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="17.6953125" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="35.90625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="13.44140625" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="11.03515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="36.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="8.51953125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="8.859375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="212.10546875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="23.9609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="214.97265625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="91.75" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="31.65234375" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="36.3046875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="93.1640625" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="29.45703125" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="33.8203125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
